--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98051</v>
+        <v>98053</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98053</v>
+        <v>98060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98060</v>
+        <v>98069</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98069</v>
+        <v>98077</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98077</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121984836</v>
       </c>
       <c r="B4" t="n">
-        <v>98117</v>
+        <v>98122</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122485273</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90854</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bärsjöberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579504</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665377</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre tallskog, lav-ristyp</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>122485273</v>
       </c>
       <c r="B5" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1357-2025 artfynd.xlsx
+++ b/artfynd/A 1357-2025 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>122485273</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
